--- a/Initial_data/2024/GeoData.xlsx
+++ b/Initial_data/2024/GeoData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t>Sample</t>
   </si>
@@ -38,7 +38,7 @@
     <t>eH</t>
   </si>
   <si>
-    <t>lattitude</t>
+    <t>latitude</t>
   </si>
   <si>
     <t>lontitude</t>
@@ -249,60 +249,6 @@
   </si>
   <si>
     <t>ADOM-SL7-13</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-BO-1</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-BO-2</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-BO-3</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-B3-1</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-B3-2</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-B3-3</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-BZ-1</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-B1-1</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-B1-2</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-B1-3</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-B1-4</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-B1-5</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-B1-6</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-B1-7</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-B1-8</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-B2-1</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-B2-2</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-B2-3</t>
   </si>
 </sst>
 </file>
@@ -1289,10 +1235,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="13.3333333333333" customWidth="1"/>
+    <col min="1" max="1" width="49.7142857142857" customWidth="1"/>
     <col min="4" max="4" width="10.5047619047619"/>
     <col min="5" max="5" width="11.6666666666667"/>
     <col min="6" max="6" width="10.5047619047619"/>
@@ -2489,312 +2435,6 @@
         <v>104.223874</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
-      <c r="A71" t="s">
-        <v>74</v>
-      </c>
-      <c r="B71">
-        <v>7.9</v>
-      </c>
-      <c r="C71">
-        <v>20</v>
-      </c>
-      <c r="D71">
-        <v>51.491945</v>
-      </c>
-      <c r="E71">
-        <v>104.239949</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" t="s">
-        <v>75</v>
-      </c>
-      <c r="B72">
-        <v>7.6</v>
-      </c>
-      <c r="C72">
-        <v>18</v>
-      </c>
-      <c r="D72">
-        <v>51.49415</v>
-      </c>
-      <c r="E72">
-        <v>104.240904</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" t="s">
-        <v>76</v>
-      </c>
-      <c r="B73">
-        <v>7.7</v>
-      </c>
-      <c r="C73">
-        <v>24</v>
-      </c>
-      <c r="D73">
-        <v>51.49575</v>
-      </c>
-      <c r="E73">
-        <v>104.241618</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" t="s">
-        <v>77</v>
-      </c>
-      <c r="B74">
-        <v>7.9</v>
-      </c>
-      <c r="C74">
-        <v>82</v>
-      </c>
-      <c r="D74">
-        <v>51.502798</v>
-      </c>
-      <c r="E74">
-        <v>104.225664</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" t="s">
-        <v>78</v>
-      </c>
-      <c r="B75">
-        <v>7.5</v>
-      </c>
-      <c r="C75">
-        <v>108</v>
-      </c>
-      <c r="D75">
-        <v>51.501383</v>
-      </c>
-      <c r="E75">
-        <v>104.230511</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" t="s">
-        <v>79</v>
-      </c>
-      <c r="B76">
-        <v>7.6</v>
-      </c>
-      <c r="C76">
-        <v>132</v>
-      </c>
-      <c r="D76">
-        <v>51.501906</v>
-      </c>
-      <c r="E76">
-        <v>104.232519</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" t="s">
-        <v>80</v>
-      </c>
-      <c r="B77">
-        <v>7.8</v>
-      </c>
-      <c r="C77">
-        <v>115</v>
-      </c>
-      <c r="D77">
-        <v>51.798149</v>
-      </c>
-      <c r="E77">
-        <v>104.365782</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" t="s">
-        <v>81</v>
-      </c>
-      <c r="B78">
-        <v>7.4</v>
-      </c>
-      <c r="C78">
-        <v>120</v>
-      </c>
-      <c r="D78">
-        <v>51.496572</v>
-      </c>
-      <c r="E78">
-        <v>104.218639</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" t="s">
-        <v>82</v>
-      </c>
-      <c r="B79">
-        <v>7.6</v>
-      </c>
-      <c r="C79">
-        <v>47</v>
-      </c>
-      <c r="D79">
-        <v>51.496572</v>
-      </c>
-      <c r="E79">
-        <v>104.218639</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" t="s">
-        <v>83</v>
-      </c>
-      <c r="B80">
-        <v>7.6</v>
-      </c>
-      <c r="C80">
-        <v>118</v>
-      </c>
-      <c r="D80">
-        <v>51.496572</v>
-      </c>
-      <c r="E80">
-        <v>104.218639</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" t="s">
-        <v>84</v>
-      </c>
-      <c r="B81">
-        <v>8.1</v>
-      </c>
-      <c r="C81">
-        <v>95</v>
-      </c>
-      <c r="D81">
-        <v>51.496572</v>
-      </c>
-      <c r="E81">
-        <v>104.218639</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" t="s">
-        <v>85</v>
-      </c>
-      <c r="B82">
-        <v>7.5</v>
-      </c>
-      <c r="C82">
-        <v>118</v>
-      </c>
-      <c r="D82">
-        <v>51.499317</v>
-      </c>
-      <c r="E82">
-        <v>104.243667</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" t="s">
-        <v>86</v>
-      </c>
-      <c r="B83">
-        <v>7.89</v>
-      </c>
-      <c r="C83">
-        <v>103</v>
-      </c>
-      <c r="D83">
-        <v>51.5004</v>
-      </c>
-      <c r="E83">
-        <v>104.243695</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" t="s">
-        <v>87</v>
-      </c>
-      <c r="B84">
-        <v>7.9</v>
-      </c>
-      <c r="C84">
-        <v>93</v>
-      </c>
-      <c r="D84">
-        <v>51.500629</v>
-      </c>
-      <c r="E84">
-        <v>104.243478</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" t="s">
-        <v>88</v>
-      </c>
-      <c r="B85">
-        <v>7.76</v>
-      </c>
-      <c r="C85">
-        <v>97</v>
-      </c>
-      <c r="D85">
-        <v>51.500566</v>
-      </c>
-      <c r="E85">
-        <v>104.243611</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" t="s">
-        <v>89</v>
-      </c>
-      <c r="B86">
-        <v>7.7</v>
-      </c>
-      <c r="C86">
-        <v>59</v>
-      </c>
-      <c r="D86">
-        <v>51.501156</v>
-      </c>
-      <c r="E86">
-        <v>104.236788</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
-      <c r="A87" t="s">
-        <v>90</v>
-      </c>
-      <c r="B87">
-        <v>7.8</v>
-      </c>
-      <c r="C87">
-        <v>60</v>
-      </c>
-      <c r="D87">
-        <v>51.501317</v>
-      </c>
-      <c r="E87">
-        <v>104.23478</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
-      <c r="A88" t="s">
-        <v>91</v>
-      </c>
-      <c r="B88">
-        <v>7.56</v>
-      </c>
-      <c r="C88">
-        <v>138</v>
-      </c>
-      <c r="D88">
-        <v>51.499904</v>
-      </c>
-      <c r="E88">
-        <v>104.236545</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
